--- a/artfynd/A 35117-2025 artfynd.xlsx
+++ b/artfynd/A 35117-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91798039</v>
+        <v>91798040</v>
       </c>
       <c r="B2" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527769.67975267</v>
+        <v>527754</v>
       </c>
       <c r="R2" t="n">
-        <v>6985358.63448944</v>
+        <v>6985490</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,19 +747,9 @@
           <t>2020-08-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-08-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,15 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91798040</v>
+        <v>104846569</v>
       </c>
       <c r="B3" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,38 +799,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Läroverket, Jmt</t>
+          <t>Björnberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527753.9951306462</v>
+        <v>527593</v>
       </c>
       <c r="R3" t="n">
-        <v>6985490.290920607</v>
+        <v>6985371</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,22 +853,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-08-12</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-08-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,14 +870,6 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AN3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -924,6 +882,119 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>91798039</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91962</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Läroverket, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>527770</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6985359</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-08-12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-08-12</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 35117-2025 artfynd.xlsx
+++ b/artfynd/A 35117-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91798040</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104846569</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,8 +1014,18 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91798039</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>